--- a/VanHanhCD1/wwwroot/templates/BMVH_QG1ThieuKet1.xlsx
+++ b/VanHanhCD1/wwwroot/templates/BMVH_QG1ThieuKet1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\03. Project Hoa Phat\07. Backend\VanHanhCD1_API-main\VanHanhCD1\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C1951F-9D03-4C0D-A846-625AF9FF6ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757E3638-FEC1-47AA-A649-A3595B2B665A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1050" windowWidth="14835" windowHeight="15150" activeTab="1" xr2:uid="{749D0495-9471-4B75-B577-F5813F33161C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{749D0495-9471-4B75-B577-F5813F33161C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -318,9 +318,6 @@
     <t>Motor_vibration_OUT_x</t>
   </si>
   <si>
-    <t>Motor_vibration_OUT_y</t>
-  </si>
-  <si>
     <t>Blower_vibration_in_X</t>
   </si>
   <si>
@@ -494,6 +491,9 @@
   </si>
   <si>
     <t>Motor_bearing_temperature_out_232A</t>
+  </si>
+  <si>
+    <t>Motor_vibration_OUT_Y</t>
   </si>
 </sst>
 </file>
@@ -890,16 +890,57 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -918,7 +959,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -937,68 +977,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1021,6 +1006,21 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1593,190 +1593,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41"/>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="S1" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
-      <c r="V1" s="43"/>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
+      <c r="A1" s="16"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="S1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
+      <c r="Y1" s="18"/>
+      <c r="Z1" s="18"/>
     </row>
     <row r="2" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
-      <c r="V2" s="45"/>
-      <c r="W2" s="45"/>
-      <c r="X2" s="45"/>
-      <c r="Y2" s="45"/>
-      <c r="Z2" s="45"/>
+      <c r="A2" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
     </row>
     <row r="3" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
-      <c r="V3" s="26"/>
-      <c r="W3" s="26"/>
-      <c r="X3" s="26"/>
-      <c r="Y3" s="26"/>
-      <c r="Z3" s="26"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="22"/>
+      <c r="T3" s="22"/>
+      <c r="U3" s="22"/>
+      <c r="V3" s="22"/>
+      <c r="W3" s="22"/>
+      <c r="X3" s="22"/>
+      <c r="Y3" s="22"/>
+      <c r="Z3" s="22"/>
     </row>
     <row r="4" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" s="33" t="s">
+      <c r="C4" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="D4" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="G4" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="H4" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="I4" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="28"/>
+    </row>
+    <row r="5" spans="1:26" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="24"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="17" t="s">
+      <c r="J5" s="27"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="M5" s="28"/>
+      <c r="N5" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="O5" s="28"/>
+      <c r="P5" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
-      <c r="T4" s="19"/>
-      <c r="U4" s="19"/>
-      <c r="V4" s="19"/>
-      <c r="W4" s="18"/>
-      <c r="X4" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y4" s="19"/>
-      <c r="Z4" s="18"/>
-    </row>
-    <row r="5" spans="1:26" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="40"/>
-      <c r="B5" s="33"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="J5" s="19"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="M5" s="18"/>
-      <c r="N5" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="O5" s="18"/>
-      <c r="P5" s="17" t="s">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="17" t="s">
+      <c r="S5" s="28"/>
+      <c r="T5" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="S5" s="18"/>
-      <c r="T5" s="17" t="s">
+      <c r="U5" s="28"/>
+      <c r="V5" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="U5" s="18"/>
-      <c r="V5" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="W5" s="18"/>
+      <c r="W5" s="28"/>
       <c r="X5" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y5" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y5" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z5" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="Z5" s="33" t="s">
-        <v>90</v>
-      </c>
     </row>
     <row r="6" spans="1:26" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="34"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
       <c r="I6" s="14" t="s">
         <v>4</v>
       </c>
@@ -1823,13 +1823,13 @@
         <v>18</v>
       </c>
       <c r="X6" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y6" s="34"/>
-      <c r="Z6" s="34"/>
+        <v>100</v>
+      </c>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="25"/>
     </row>
     <row r="7" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="39"/>
+      <c r="A7" s="33"/>
       <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
@@ -1931,7 +1931,7 @@
       </c>
     </row>
     <row r="8" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="35"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="1" t="s">
         <v>20</v>
       </c>
@@ -2033,7 +2033,7 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="35"/>
+      <c r="A9" s="29"/>
       <c r="B9" s="1" t="s">
         <v>21</v>
       </c>
@@ -2135,7 +2135,7 @@
       </c>
     </row>
     <row r="10" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="35"/>
+      <c r="A10" s="29"/>
       <c r="B10" s="1" t="s">
         <v>22</v>
       </c>
@@ -2237,7 +2237,7 @@
       </c>
     </row>
     <row r="11" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="35"/>
+      <c r="A11" s="29"/>
       <c r="B11" s="1" t="s">
         <v>23</v>
       </c>
@@ -2339,7 +2339,7 @@
       </c>
     </row>
     <row r="12" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="35"/>
+      <c r="A12" s="29"/>
       <c r="B12" s="1" t="s">
         <v>24</v>
       </c>
@@ -2441,7 +2441,7 @@
       </c>
     </row>
     <row r="13" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
+      <c r="A13" s="29"/>
       <c r="B13" s="1" t="s">
         <v>25</v>
       </c>
@@ -2543,7 +2543,7 @@
       </c>
     </row>
     <row r="14" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="35"/>
+      <c r="A14" s="29"/>
       <c r="B14" s="1" t="s">
         <v>26</v>
       </c>
@@ -2645,7 +2645,7 @@
       </c>
     </row>
     <row r="15" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="35"/>
+      <c r="A15" s="29"/>
       <c r="B15" s="1" t="s">
         <v>27</v>
       </c>
@@ -2747,7 +2747,7 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="35"/>
+      <c r="A16" s="29"/>
       <c r="B16" s="3" t="s">
         <v>28</v>
       </c>
@@ -2849,7 +2849,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="35"/>
+      <c r="A17" s="29"/>
       <c r="B17" s="3" t="s">
         <v>29</v>
       </c>
@@ -2951,7 +2951,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="35"/>
+      <c r="A18" s="29"/>
       <c r="B18" s="3" t="s">
         <v>30</v>
       </c>
@@ -3053,7 +3053,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="35"/>
+      <c r="A19" s="29"/>
       <c r="B19" s="3" t="s">
         <v>31</v>
       </c>
@@ -3155,7 +3155,7 @@
       </c>
     </row>
     <row r="20" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="35"/>
+      <c r="A20" s="29"/>
       <c r="B20" s="3" t="s">
         <v>32</v>
       </c>
@@ -3257,7 +3257,7 @@
       </c>
     </row>
     <row r="21" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="35"/>
+      <c r="A21" s="29"/>
       <c r="B21" s="3" t="s">
         <v>33</v>
       </c>
@@ -3359,7 +3359,7 @@
       </c>
     </row>
     <row r="22" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="35"/>
+      <c r="A22" s="29"/>
       <c r="B22" s="3" t="s">
         <v>34</v>
       </c>
@@ -3461,7 +3461,7 @@
       </c>
     </row>
     <row r="23" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="35"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="3" t="s">
         <v>35</v>
       </c>
@@ -3563,7 +3563,7 @@
       </c>
     </row>
     <row r="24" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="35"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="3" t="s">
         <v>36</v>
       </c>
@@ -3665,7 +3665,7 @@
       </c>
     </row>
     <row r="25" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="35"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="3" t="s">
         <v>37</v>
       </c>
@@ -3767,7 +3767,7 @@
       </c>
     </row>
     <row r="26" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="35"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="3" t="s">
         <v>38</v>
       </c>
@@ -3869,7 +3869,7 @@
       </c>
     </row>
     <row r="27" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="35"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="3" t="s">
         <v>39</v>
       </c>
@@ -3971,7 +3971,7 @@
       </c>
     </row>
     <row r="28" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="35"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="3" t="s">
         <v>40</v>
       </c>
@@ -4073,7 +4073,7 @@
       </c>
     </row>
     <row r="29" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="35"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="3" t="s">
         <v>41</v>
       </c>
@@ -4175,7 +4175,7 @@
       </c>
     </row>
     <row r="30" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="36"/>
+      <c r="A30" s="30"/>
       <c r="B30" s="3" t="s">
         <v>42</v>
       </c>
@@ -4277,173 +4277,199 @@
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A31" s="37" t="s">
+      <c r="A31" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="38"/>
-      <c r="C31" s="38"/>
-      <c r="D31" s="38"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
-      <c r="J31" s="38"/>
-      <c r="K31" s="38"/>
-      <c r="L31" s="38"/>
-      <c r="M31" s="38"/>
-      <c r="N31" s="38"/>
-      <c r="O31" s="38"/>
-      <c r="P31" s="38"/>
-      <c r="Q31" s="38"/>
-      <c r="R31" s="38"/>
-      <c r="S31" s="38"/>
-      <c r="T31" s="38"/>
-      <c r="U31" s="38"/>
-      <c r="V31" s="38"/>
-      <c r="W31" s="38"/>
-      <c r="X31" s="38"/>
-      <c r="Y31" s="38"/>
-      <c r="Z31" s="38"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="32"/>
+      <c r="L31" s="32"/>
+      <c r="M31" s="32"/>
+      <c r="N31" s="32"/>
+      <c r="O31" s="32"/>
+      <c r="P31" s="32"/>
+      <c r="Q31" s="32"/>
+      <c r="R31" s="32"/>
+      <c r="S31" s="32"/>
+      <c r="T31" s="32"/>
+      <c r="U31" s="32"/>
+      <c r="V31" s="32"/>
+      <c r="W31" s="32"/>
+      <c r="X31" s="32"/>
+      <c r="Y31" s="32"/>
+      <c r="Z31" s="32"/>
     </row>
     <row r="32" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="17" t="s">
+      <c r="B32" s="42"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="17" t="s">
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="27" t="s">
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="27"/>
+      <c r="N32" s="27"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="17" t="s">
+      <c r="Q32" s="42"/>
+      <c r="R32" s="43"/>
+      <c r="S32" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="T32" s="19"/>
-      <c r="U32" s="19"/>
-      <c r="V32" s="19"/>
-      <c r="W32" s="19"/>
-      <c r="X32" s="16" t="s">
+      <c r="T32" s="27"/>
+      <c r="U32" s="27"/>
+      <c r="V32" s="27"/>
+      <c r="W32" s="27"/>
+      <c r="X32" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="Y32" s="16"/>
-      <c r="Z32" s="16"/>
+      <c r="Y32" s="34"/>
+      <c r="Z32" s="34"/>
     </row>
     <row r="33" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="30"/>
-      <c r="B33" s="31"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="17" t="s">
+      <c r="A33" s="44"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="E33" s="18"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="17" t="s">
+      <c r="E33" s="28"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="K33" s="18"/>
-      <c r="L33" s="22"/>
-      <c r="M33" s="23"/>
-      <c r="N33" s="23"/>
-      <c r="O33" s="24"/>
-      <c r="P33" s="30"/>
-      <c r="Q33" s="31"/>
-      <c r="R33" s="32"/>
-      <c r="S33" s="17" t="s">
+      <c r="K33" s="28"/>
+      <c r="L33" s="37"/>
+      <c r="M33" s="38"/>
+      <c r="N33" s="38"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="44"/>
+      <c r="Q33" s="45"/>
+      <c r="R33" s="46"/>
+      <c r="S33" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="T33" s="18"/>
-      <c r="U33" s="22"/>
-      <c r="V33" s="23"/>
-      <c r="W33" s="24"/>
+      <c r="T33" s="28"/>
+      <c r="U33" s="37"/>
+      <c r="V33" s="38"/>
+      <c r="W33" s="39"/>
       <c r="X33" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="Y33" s="22"/>
-      <c r="Z33" s="24"/>
+      <c r="Y33" s="37"/>
+      <c r="Z33" s="39"/>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="26"/>
-      <c r="O34" s="26"/>
-      <c r="P34" s="26"/>
-      <c r="Q34" s="26"/>
-      <c r="R34" s="26"/>
-      <c r="S34" s="26"/>
-      <c r="T34" s="26"/>
-      <c r="U34" s="26"/>
-      <c r="V34" s="26"/>
-      <c r="W34" s="26"/>
-      <c r="X34" s="26"/>
-      <c r="Y34" s="26"/>
-      <c r="Z34" s="26"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22"/>
+      <c r="R34" s="22"/>
+      <c r="S34" s="22"/>
+      <c r="T34" s="22"/>
+      <c r="U34" s="22"/>
+      <c r="V34" s="22"/>
+      <c r="W34" s="22"/>
+      <c r="X34" s="22"/>
+      <c r="Y34" s="22"/>
+      <c r="Z34" s="22"/>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A35" s="20" t="s">
+      <c r="A35" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="21"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="21"/>
-      <c r="M35" s="21"/>
-      <c r="N35" s="21"/>
-      <c r="O35" s="21"/>
-      <c r="P35" s="21"/>
-      <c r="Q35" s="21"/>
-      <c r="R35" s="21"/>
-      <c r="S35" s="21"/>
-      <c r="T35" s="21"/>
-      <c r="U35" s="21"/>
-      <c r="V35" s="21"/>
-      <c r="W35" s="21"/>
-      <c r="X35" s="21"/>
-      <c r="Y35" s="21"/>
-      <c r="Z35" s="21"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="36"/>
+      <c r="J35" s="36"/>
+      <c r="K35" s="36"/>
+      <c r="L35" s="36"/>
+      <c r="M35" s="36"/>
+      <c r="N35" s="36"/>
+      <c r="O35" s="36"/>
+      <c r="P35" s="36"/>
+      <c r="Q35" s="36"/>
+      <c r="R35" s="36"/>
+      <c r="S35" s="36"/>
+      <c r="T35" s="36"/>
+      <c r="U35" s="36"/>
+      <c r="V35" s="36"/>
+      <c r="W35" s="36"/>
+      <c r="X35" s="36"/>
+      <c r="Y35" s="36"/>
+      <c r="Z35" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="X32:Z32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="A35:Z35"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="L33:O33"/>
+    <mergeCell ref="S33:T33"/>
+    <mergeCell ref="U33:W33"/>
+    <mergeCell ref="Y33:Z33"/>
+    <mergeCell ref="A34:Z34"/>
+    <mergeCell ref="A32:C33"/>
+    <mergeCell ref="D32:I32"/>
+    <mergeCell ref="J32:O32"/>
+    <mergeCell ref="P32:R33"/>
+    <mergeCell ref="S32:W32"/>
+    <mergeCell ref="Y5:Y6"/>
+    <mergeCell ref="Z5:Z6"/>
+    <mergeCell ref="A19:A30"/>
+    <mergeCell ref="A31:Z31"/>
+    <mergeCell ref="A7:A18"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="I4:O4"/>
+    <mergeCell ref="P4:W4"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:W5"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="S1:Z1"/>
     <mergeCell ref="A2:Z2"/>
@@ -4460,32 +4486,6 @@
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="P5:Q5"/>
     <mergeCell ref="R5:S5"/>
-    <mergeCell ref="Y5:Y6"/>
-    <mergeCell ref="Z5:Z6"/>
-    <mergeCell ref="A19:A30"/>
-    <mergeCell ref="A31:Z31"/>
-    <mergeCell ref="A7:A18"/>
-    <mergeCell ref="G4:G6"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="I4:O4"/>
-    <mergeCell ref="P4:W4"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="X32:Z32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:I33"/>
-    <mergeCell ref="A35:Z35"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="L33:O33"/>
-    <mergeCell ref="S33:T33"/>
-    <mergeCell ref="U33:W33"/>
-    <mergeCell ref="Y33:Z33"/>
-    <mergeCell ref="A34:Z34"/>
-    <mergeCell ref="A32:C33"/>
-    <mergeCell ref="D32:I32"/>
-    <mergeCell ref="J32:O32"/>
-    <mergeCell ref="P32:R33"/>
-    <mergeCell ref="S32:W32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4504,10 +4504,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="55"/>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
+      <c r="A1" s="50"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
@@ -4522,60 +4522,60 @@
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
-      <c r="S1" s="56" t="s">
+      <c r="S1" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="T1" s="51"/>
+      <c r="U1" s="51"/>
+      <c r="V1" s="51"/>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A2" s="50"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="55"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="57" t="s">
-        <v>105</v>
-      </c>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="58" t="s">
-        <v>92</v>
-      </c>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
+      <c r="V2" s="53"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="55"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="52"/>
+      <c r="P3" s="52"/>
+      <c r="Q3" s="52"/>
+      <c r="R3" s="52"/>
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
@@ -4601,20 +4601,20 @@
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
       <c r="S4" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T4" s="7"/>
       <c r="U4" s="7"/>
       <c r="V4" s="7"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="55"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="8" t="s">
         <v>94</v>
-      </c>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="8" t="s">
-        <v>95</v>
       </c>
       <c r="E5" s="11">
         <v>0.33333333333333331</v>
@@ -4690,11 +4690,11 @@
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="51"/>
+      <c r="A6" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="48"/>
+      <c r="C6" s="49"/>
       <c r="D6" s="10" t="s">
         <v>51</v>
       </c>
@@ -4726,11 +4726,11 @@
       <c r="AB6" s="9"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="50" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="51"/>
+      <c r="A7" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="48"/>
+      <c r="C7" s="49"/>
       <c r="D7" s="10" t="s">
         <v>52</v>
       </c>
@@ -4760,11 +4760,11 @@
       <c r="AB7" s="9"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="24"/>
+      <c r="A8" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="38"/>
+      <c r="C8" s="39"/>
       <c r="D8" s="10" t="s">
         <v>53</v>
       </c>
@@ -4794,11 +4794,11 @@
       <c r="AB8" s="9"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="24"/>
+      <c r="A9" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="38"/>
+      <c r="C9" s="39"/>
       <c r="D9" s="10" t="s">
         <v>54</v>
       </c>
@@ -4828,11 +4828,11 @@
       <c r="AB9" s="9"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="24"/>
+      <c r="A10" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" s="38"/>
+      <c r="C10" s="39"/>
       <c r="D10" s="10" t="s">
         <v>55</v>
       </c>
@@ -4862,11 +4862,11 @@
       <c r="AB10" s="9"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="24"/>
+      <c r="A11" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="38"/>
+      <c r="C11" s="39"/>
       <c r="D11" s="10" t="s">
         <v>56</v>
       </c>
@@ -4896,11 +4896,11 @@
       <c r="AB11" s="9"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="B12" s="47" t="s">
-        <v>79</v>
+      <c r="A12" s="57" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="57" t="s">
+        <v>78</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>4</v>
@@ -4934,8 +4934,8 @@
       <c r="AB12" s="9"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="49"/>
-      <c r="B13" s="49"/>
+      <c r="A13" s="58"/>
+      <c r="B13" s="58"/>
       <c r="C13" s="9" t="s">
         <v>5</v>
       </c>
@@ -4968,8 +4968,8 @@
       <c r="AB13" s="9"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="49"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="58"/>
+      <c r="B14" s="59"/>
       <c r="C14" s="9" t="s">
         <v>6</v>
       </c>
@@ -5002,9 +5002,9 @@
       <c r="AB14" s="9"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="49"/>
-      <c r="B15" s="47" t="s">
-        <v>80</v>
+      <c r="A15" s="58"/>
+      <c r="B15" s="57" t="s">
+        <v>79</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>7</v>
@@ -5038,13 +5038,13 @@
       <c r="AB15" s="9"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A16" s="49"/>
-      <c r="B16" s="48"/>
+      <c r="A16" s="58"/>
+      <c r="B16" s="59"/>
       <c r="C16" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
@@ -5072,9 +5072,9 @@
       <c r="AB16" s="9"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A17" s="49"/>
-      <c r="B17" s="47" t="s">
-        <v>81</v>
+      <c r="A17" s="58"/>
+      <c r="B17" s="57" t="s">
+        <v>80</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>9</v>
@@ -5108,8 +5108,8 @@
       <c r="AB17" s="9"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
+      <c r="A18" s="59"/>
+      <c r="B18" s="59"/>
       <c r="C18" s="9" t="s">
         <v>10</v>
       </c>
@@ -5142,11 +5142,11 @@
       <c r="AB18" s="9"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="57" t="s">
         <v>82</v>
-      </c>
-      <c r="B19" s="47" t="s">
-        <v>83</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>11</v>
@@ -5180,8 +5180,8 @@
       <c r="AB19" s="9"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A20" s="49"/>
-      <c r="B20" s="48"/>
+      <c r="A20" s="58"/>
+      <c r="B20" s="59"/>
       <c r="C20" s="9" t="s">
         <v>12</v>
       </c>
@@ -5214,9 +5214,9 @@
       <c r="AB20" s="9"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A21" s="49"/>
-      <c r="B21" s="47" t="s">
-        <v>84</v>
+      <c r="A21" s="58"/>
+      <c r="B21" s="57" t="s">
+        <v>83</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>13</v>
@@ -5250,13 +5250,13 @@
       <c r="AB21" s="9"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A22" s="49"/>
-      <c r="B22" s="48"/>
+      <c r="A22" s="58"/>
+      <c r="B22" s="59"/>
       <c r="C22" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
@@ -5284,15 +5284,15 @@
       <c r="AB22" s="9"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A23" s="49"/>
-      <c r="B23" s="47" t="s">
-        <v>85</v>
+      <c r="A23" s="58"/>
+      <c r="B23" s="57" t="s">
+        <v>84</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>15</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
@@ -5320,13 +5320,13 @@
       <c r="AB23" s="9"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A24" s="49"/>
-      <c r="B24" s="48"/>
+      <c r="A24" s="58"/>
+      <c r="B24" s="59"/>
       <c r="C24" s="9" t="s">
         <v>16</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
@@ -5354,15 +5354,15 @@
       <c r="AB24" s="9"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A25" s="49"/>
-      <c r="B25" s="47" t="s">
-        <v>86</v>
+      <c r="A25" s="58"/>
+      <c r="B25" s="57" t="s">
+        <v>85</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
@@ -5390,13 +5390,13 @@
       <c r="AB25" s="9"/>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
+      <c r="A26" s="59"/>
+      <c r="B26" s="59"/>
       <c r="C26" s="9" t="s">
         <v>18</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
@@ -5424,15 +5424,15 @@
       <c r="AB26" s="9"/>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="57" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="51"/>
+      <c r="C27" s="49"/>
       <c r="D27" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
@@ -5460,13 +5460,13 @@
       <c r="AB27" s="9"/>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A28" s="49"/>
-      <c r="B28" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="C28" s="24"/>
+      <c r="A28" s="58"/>
+      <c r="B28" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="39"/>
       <c r="D28" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
@@ -5494,13 +5494,13 @@
       <c r="AB28" s="9"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A29" s="48"/>
-      <c r="B29" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" s="53"/>
+      <c r="A29" s="59"/>
+      <c r="B29" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="61"/>
       <c r="D29" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
@@ -5529,12 +5529,15 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A1:D3"/>
-    <mergeCell ref="S1:V1"/>
-    <mergeCell ref="F2:R3"/>
-    <mergeCell ref="S2:V2"/>
-    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
     <mergeCell ref="A12:A18"/>
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="B15:B16"/>
@@ -5542,17 +5545,14 @@
     <mergeCell ref="A19:A26"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="B21:B22"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="B25:B26"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A1:D3"/>
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="F2:R3"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="A5:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/VanHanhCD1/wwwroot/templates/BMVH_QG1ThieuKet1.xlsx
+++ b/VanHanhCD1/wwwroot/templates/BMVH_QG1ThieuKet1.xlsx
@@ -5,21 +5,30 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\03. Project Hoa Phat\07. Backend\VanHanhCD1_API-main\VanHanhCD1\wwwroot\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02. Du An Hoa Phat\API\VanHanhCD1_API-release\VanHanhCD1\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757E3638-FEC1-47AA-A649-A3595B2B665A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA1776B-D451-477C-B7DA-2BE5CAA121A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{749D0495-9471-4B75-B577-F5813F33161C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{749D0495-9471-4B75-B577-F5813F33161C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -890,6 +899,75 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -908,82 +986,28 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1006,21 +1030,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1579,7 +1588,7 @@
   <dimension ref="A1:Z35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.85546875" bestFit="1" customWidth="1"/>
@@ -1593,190 +1602,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="S1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="18"/>
-      <c r="Z1" s="18"/>
+      <c r="A1" s="41"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="S1" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="43"/>
     </row>
     <row r="2" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="V2" s="20"/>
-      <c r="W2" s="20"/>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="20"/>
-      <c r="Z2" s="20"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
+      <c r="V2" s="45"/>
+      <c r="W2" s="45"/>
+      <c r="X2" s="45"/>
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="45"/>
     </row>
     <row r="3" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="22"/>
-      <c r="V3" s="22"/>
-      <c r="W3" s="22"/>
-      <c r="X3" s="22"/>
-      <c r="Y3" s="22"/>
-      <c r="Z3" s="22"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
+      <c r="V3" s="26"/>
+      <c r="W3" s="26"/>
+      <c r="X3" s="26"/>
+      <c r="Y3" s="26"/>
+      <c r="Z3" s="26"/>
     </row>
     <row r="4" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H4" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I4" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="26" t="s">
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="27"/>
-      <c r="T4" s="27"/>
-      <c r="U4" s="27"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="28"/>
-      <c r="X4" s="26" t="s">
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="19"/>
+      <c r="V4" s="19"/>
+      <c r="W4" s="18"/>
+      <c r="X4" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="Y4" s="27"/>
-      <c r="Z4" s="28"/>
+      <c r="Y4" s="19"/>
+      <c r="Z4" s="18"/>
     </row>
     <row r="5" spans="1:26" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="26" t="s">
+      <c r="A5" s="40"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="J5" s="27"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="26" t="s">
+      <c r="J5" s="19"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="M5" s="28"/>
-      <c r="N5" s="26" t="s">
+      <c r="M5" s="18"/>
+      <c r="N5" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="O5" s="28"/>
-      <c r="P5" s="26" t="s">
+      <c r="O5" s="18"/>
+      <c r="P5" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="26" t="s">
+      <c r="Q5" s="18"/>
+      <c r="R5" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="S5" s="28"/>
-      <c r="T5" s="26" t="s">
+      <c r="S5" s="18"/>
+      <c r="T5" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="U5" s="28"/>
-      <c r="V5" s="26" t="s">
+      <c r="U5" s="18"/>
+      <c r="V5" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="W5" s="28"/>
+      <c r="W5" s="18"/>
       <c r="X5" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="Y5" s="23" t="s">
+      <c r="Y5" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="Z5" s="23" t="s">
+      <c r="Z5" s="33" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="25"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
+      <c r="A6" s="34"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
       <c r="I6" s="14" t="s">
         <v>4</v>
       </c>
@@ -1825,11 +1834,11 @@
       <c r="X6" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="Y6" s="25"/>
-      <c r="Z6" s="25"/>
+      <c r="Y6" s="34"/>
+      <c r="Z6" s="34"/>
     </row>
     <row r="7" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="33"/>
+      <c r="A7" s="39"/>
       <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
@@ -1931,7 +1940,7 @@
       </c>
     </row>
     <row r="8" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="29"/>
+      <c r="A8" s="35"/>
       <c r="B8" s="1" t="s">
         <v>20</v>
       </c>
@@ -2033,7 +2042,7 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="29"/>
+      <c r="A9" s="35"/>
       <c r="B9" s="1" t="s">
         <v>21</v>
       </c>
@@ -2135,7 +2144,7 @@
       </c>
     </row>
     <row r="10" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="29"/>
+      <c r="A10" s="35"/>
       <c r="B10" s="1" t="s">
         <v>22</v>
       </c>
@@ -2237,7 +2246,7 @@
       </c>
     </row>
     <row r="11" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="29"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="1" t="s">
         <v>23</v>
       </c>
@@ -2339,7 +2348,7 @@
       </c>
     </row>
     <row r="12" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="29"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="1" t="s">
         <v>24</v>
       </c>
@@ -2441,7 +2450,7 @@
       </c>
     </row>
     <row r="13" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="29"/>
+      <c r="A13" s="35"/>
       <c r="B13" s="1" t="s">
         <v>25</v>
       </c>
@@ -2543,7 +2552,7 @@
       </c>
     </row>
     <row r="14" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="29"/>
+      <c r="A14" s="35"/>
       <c r="B14" s="1" t="s">
         <v>26</v>
       </c>
@@ -2645,7 +2654,7 @@
       </c>
     </row>
     <row r="15" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="29"/>
+      <c r="A15" s="35"/>
       <c r="B15" s="1" t="s">
         <v>27</v>
       </c>
@@ -2747,7 +2756,7 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="29"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="3" t="s">
         <v>28</v>
       </c>
@@ -2849,7 +2858,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="29"/>
+      <c r="A17" s="35"/>
       <c r="B17" s="3" t="s">
         <v>29</v>
       </c>
@@ -2951,7 +2960,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="29"/>
+      <c r="A18" s="35"/>
       <c r="B18" s="3" t="s">
         <v>30</v>
       </c>
@@ -3053,7 +3062,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="29"/>
+      <c r="A19" s="35"/>
       <c r="B19" s="3" t="s">
         <v>31</v>
       </c>
@@ -3155,7 +3164,7 @@
       </c>
     </row>
     <row r="20" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="29"/>
+      <c r="A20" s="35"/>
       <c r="B20" s="3" t="s">
         <v>32</v>
       </c>
@@ -3257,7 +3266,7 @@
       </c>
     </row>
     <row r="21" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="29"/>
+      <c r="A21" s="35"/>
       <c r="B21" s="3" t="s">
         <v>33</v>
       </c>
@@ -3359,7 +3368,7 @@
       </c>
     </row>
     <row r="22" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="29"/>
+      <c r="A22" s="35"/>
       <c r="B22" s="3" t="s">
         <v>34</v>
       </c>
@@ -3461,7 +3470,7 @@
       </c>
     </row>
     <row r="23" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="29"/>
+      <c r="A23" s="35"/>
       <c r="B23" s="3" t="s">
         <v>35</v>
       </c>
@@ -3563,7 +3572,7 @@
       </c>
     </row>
     <row r="24" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="29"/>
+      <c r="A24" s="35"/>
       <c r="B24" s="3" t="s">
         <v>36</v>
       </c>
@@ -3665,7 +3674,7 @@
       </c>
     </row>
     <row r="25" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="29"/>
+      <c r="A25" s="35"/>
       <c r="B25" s="3" t="s">
         <v>37</v>
       </c>
@@ -3767,7 +3776,7 @@
       </c>
     </row>
     <row r="26" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="29"/>
+      <c r="A26" s="35"/>
       <c r="B26" s="3" t="s">
         <v>38</v>
       </c>
@@ -3869,7 +3878,7 @@
       </c>
     </row>
     <row r="27" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="29"/>
+      <c r="A27" s="35"/>
       <c r="B27" s="3" t="s">
         <v>39</v>
       </c>
@@ -3971,7 +3980,7 @@
       </c>
     </row>
     <row r="28" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="29"/>
+      <c r="A28" s="35"/>
       <c r="B28" s="3" t="s">
         <v>40</v>
       </c>
@@ -4073,7 +4082,7 @@
       </c>
     </row>
     <row r="29" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="29"/>
+      <c r="A29" s="35"/>
       <c r="B29" s="3" t="s">
         <v>41</v>
       </c>
@@ -4175,7 +4184,7 @@
       </c>
     </row>
     <row r="30" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="30"/>
+      <c r="A30" s="36"/>
       <c r="B30" s="3" t="s">
         <v>42</v>
       </c>
@@ -4277,199 +4286,173 @@
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="32"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="32"/>
-      <c r="K31" s="32"/>
-      <c r="L31" s="32"/>
-      <c r="M31" s="32"/>
-      <c r="N31" s="32"/>
-      <c r="O31" s="32"/>
-      <c r="P31" s="32"/>
-      <c r="Q31" s="32"/>
-      <c r="R31" s="32"/>
-      <c r="S31" s="32"/>
-      <c r="T31" s="32"/>
-      <c r="U31" s="32"/>
-      <c r="V31" s="32"/>
-      <c r="W31" s="32"/>
-      <c r="X31" s="32"/>
-      <c r="Y31" s="32"/>
-      <c r="Z31" s="32"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="38"/>
+      <c r="K31" s="38"/>
+      <c r="L31" s="38"/>
+      <c r="M31" s="38"/>
+      <c r="N31" s="38"/>
+      <c r="O31" s="38"/>
+      <c r="P31" s="38"/>
+      <c r="Q31" s="38"/>
+      <c r="R31" s="38"/>
+      <c r="S31" s="38"/>
+      <c r="T31" s="38"/>
+      <c r="U31" s="38"/>
+      <c r="V31" s="38"/>
+      <c r="W31" s="38"/>
+      <c r="X31" s="38"/>
+      <c r="Y31" s="38"/>
+      <c r="Z31" s="38"/>
     </row>
     <row r="32" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="41" t="s">
+      <c r="A32" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="42"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="26" t="s">
+      <c r="B32" s="28"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="26" t="s">
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="K32" s="27"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="27"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="41" t="s">
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="Q32" s="42"/>
-      <c r="R32" s="43"/>
-      <c r="S32" s="26" t="s">
+      <c r="Q32" s="28"/>
+      <c r="R32" s="29"/>
+      <c r="S32" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="T32" s="27"/>
-      <c r="U32" s="27"/>
-      <c r="V32" s="27"/>
-      <c r="W32" s="27"/>
-      <c r="X32" s="34" t="s">
+      <c r="T32" s="19"/>
+      <c r="U32" s="19"/>
+      <c r="V32" s="19"/>
+      <c r="W32" s="19"/>
+      <c r="X32" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="Y32" s="34"/>
-      <c r="Z32" s="34"/>
+      <c r="Y32" s="16"/>
+      <c r="Z32" s="16"/>
     </row>
     <row r="33" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="44"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="26" t="s">
+      <c r="A33" s="30"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E33" s="28"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="26" t="s">
+      <c r="E33" s="18"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="K33" s="28"/>
-      <c r="L33" s="37"/>
-      <c r="M33" s="38"/>
-      <c r="N33" s="38"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="44"/>
-      <c r="Q33" s="45"/>
-      <c r="R33" s="46"/>
-      <c r="S33" s="26" t="s">
+      <c r="K33" s="18"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="23"/>
+      <c r="N33" s="23"/>
+      <c r="O33" s="24"/>
+      <c r="P33" s="30"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="T33" s="28"/>
-      <c r="U33" s="37"/>
-      <c r="V33" s="38"/>
-      <c r="W33" s="39"/>
+      <c r="T33" s="18"/>
+      <c r="U33" s="22"/>
+      <c r="V33" s="23"/>
+      <c r="W33" s="24"/>
       <c r="X33" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="Y33" s="37"/>
-      <c r="Z33" s="39"/>
+      <c r="Y33" s="22"/>
+      <c r="Z33" s="24"/>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A34" s="40" t="s">
+      <c r="A34" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="22"/>
-      <c r="L34" s="22"/>
-      <c r="M34" s="22"/>
-      <c r="N34" s="22"/>
-      <c r="O34" s="22"/>
-      <c r="P34" s="22"/>
-      <c r="Q34" s="22"/>
-      <c r="R34" s="22"/>
-      <c r="S34" s="22"/>
-      <c r="T34" s="22"/>
-      <c r="U34" s="22"/>
-      <c r="V34" s="22"/>
-      <c r="W34" s="22"/>
-      <c r="X34" s="22"/>
-      <c r="Y34" s="22"/>
-      <c r="Z34" s="22"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="26"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="26"/>
+      <c r="O34" s="26"/>
+      <c r="P34" s="26"/>
+      <c r="Q34" s="26"/>
+      <c r="R34" s="26"/>
+      <c r="S34" s="26"/>
+      <c r="T34" s="26"/>
+      <c r="U34" s="26"/>
+      <c r="V34" s="26"/>
+      <c r="W34" s="26"/>
+      <c r="X34" s="26"/>
+      <c r="Y34" s="26"/>
+      <c r="Z34" s="26"/>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A35" s="35" t="s">
+      <c r="A35" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
-      <c r="J35" s="36"/>
-      <c r="K35" s="36"/>
-      <c r="L35" s="36"/>
-      <c r="M35" s="36"/>
-      <c r="N35" s="36"/>
-      <c r="O35" s="36"/>
-      <c r="P35" s="36"/>
-      <c r="Q35" s="36"/>
-      <c r="R35" s="36"/>
-      <c r="S35" s="36"/>
-      <c r="T35" s="36"/>
-      <c r="U35" s="36"/>
-      <c r="V35" s="36"/>
-      <c r="W35" s="36"/>
-      <c r="X35" s="36"/>
-      <c r="Y35" s="36"/>
-      <c r="Z35" s="36"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="21"/>
+      <c r="O35" s="21"/>
+      <c r="P35" s="21"/>
+      <c r="Q35" s="21"/>
+      <c r="R35" s="21"/>
+      <c r="S35" s="21"/>
+      <c r="T35" s="21"/>
+      <c r="U35" s="21"/>
+      <c r="V35" s="21"/>
+      <c r="W35" s="21"/>
+      <c r="X35" s="21"/>
+      <c r="Y35" s="21"/>
+      <c r="Z35" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="X32:Z32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:I33"/>
-    <mergeCell ref="A35:Z35"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="L33:O33"/>
-    <mergeCell ref="S33:T33"/>
-    <mergeCell ref="U33:W33"/>
-    <mergeCell ref="Y33:Z33"/>
-    <mergeCell ref="A34:Z34"/>
-    <mergeCell ref="A32:C33"/>
-    <mergeCell ref="D32:I32"/>
-    <mergeCell ref="J32:O32"/>
-    <mergeCell ref="P32:R33"/>
-    <mergeCell ref="S32:W32"/>
-    <mergeCell ref="Y5:Y6"/>
-    <mergeCell ref="Z5:Z6"/>
-    <mergeCell ref="A19:A30"/>
-    <mergeCell ref="A31:Z31"/>
-    <mergeCell ref="A7:A18"/>
-    <mergeCell ref="G4:G6"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="I4:O4"/>
-    <mergeCell ref="P4:W4"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="V5:W5"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="S1:Z1"/>
     <mergeCell ref="A2:Z2"/>
@@ -4486,6 +4469,32 @@
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="P5:Q5"/>
     <mergeCell ref="R5:S5"/>
+    <mergeCell ref="Y5:Y6"/>
+    <mergeCell ref="Z5:Z6"/>
+    <mergeCell ref="A19:A30"/>
+    <mergeCell ref="A31:Z31"/>
+    <mergeCell ref="A7:A18"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="I4:O4"/>
+    <mergeCell ref="P4:W4"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="X32:Z32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="A35:Z35"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="L33:O33"/>
+    <mergeCell ref="S33:T33"/>
+    <mergeCell ref="U33:W33"/>
+    <mergeCell ref="Y33:Z33"/>
+    <mergeCell ref="A34:Z34"/>
+    <mergeCell ref="A32:C33"/>
+    <mergeCell ref="D32:I32"/>
+    <mergeCell ref="J32:O32"/>
+    <mergeCell ref="P32:R33"/>
+    <mergeCell ref="S32:W32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4504,10 +4513,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="50"/>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
+      <c r="A1" s="55"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
@@ -4522,60 +4531,60 @@
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
-      <c r="S1" s="51" t="s">
+      <c r="S1" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="50"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52"/>
-      <c r="O2" s="52"/>
-      <c r="P2" s="52"/>
-      <c r="Q2" s="52"/>
-      <c r="R2" s="52"/>
-      <c r="S2" s="53" t="s">
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="57"/>
+      <c r="Q2" s="57"/>
+      <c r="R2" s="57"/>
+      <c r="S2" s="58" t="s">
         <v>91</v>
       </c>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
-      <c r="V2" s="53"/>
+      <c r="T2" s="58"/>
+      <c r="U2" s="58"/>
+      <c r="V2" s="58"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="50"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
+      <c r="A3" s="55"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="52"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
@@ -4608,11 +4617,11 @@
       <c r="V4" s="7"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="56"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
       <c r="D5" s="8" t="s">
         <v>94</v>
       </c>
@@ -4690,11 +4699,11 @@
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="49"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="51"/>
       <c r="D6" s="10" t="s">
         <v>51</v>
       </c>
@@ -4726,11 +4735,11 @@
       <c r="AB6" s="9"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="49"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="51"/>
       <c r="D7" s="10" t="s">
         <v>52</v>
       </c>
@@ -4760,11 +4769,11 @@
       <c r="AB7" s="9"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="39"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="24"/>
       <c r="D8" s="10" t="s">
         <v>53</v>
       </c>
@@ -4794,11 +4803,11 @@
       <c r="AB8" s="9"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="38"/>
-      <c r="C9" s="39"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="24"/>
       <c r="D9" s="10" t="s">
         <v>54</v>
       </c>
@@ -4828,11 +4837,11 @@
       <c r="AB9" s="9"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="39"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="24"/>
       <c r="D10" s="10" t="s">
         <v>55</v>
       </c>
@@ -4862,11 +4871,11 @@
       <c r="AB10" s="9"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="38"/>
-      <c r="C11" s="39"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="24"/>
       <c r="D11" s="10" t="s">
         <v>56</v>
       </c>
@@ -4896,10 +4905,10 @@
       <c r="AB11" s="9"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="57" t="s">
+      <c r="A12" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="57" t="s">
+      <c r="B12" s="47" t="s">
         <v>78</v>
       </c>
       <c r="C12" s="9" t="s">
@@ -4934,8 +4943,8 @@
       <c r="AB12" s="9"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="58"/>
-      <c r="B13" s="58"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
       <c r="C13" s="9" t="s">
         <v>5</v>
       </c>
@@ -4968,8 +4977,8 @@
       <c r="AB13" s="9"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="58"/>
-      <c r="B14" s="59"/>
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
       <c r="C14" s="9" t="s">
         <v>6</v>
       </c>
@@ -5002,8 +5011,8 @@
       <c r="AB14" s="9"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="58"/>
-      <c r="B15" s="57" t="s">
+      <c r="A15" s="48"/>
+      <c r="B15" s="47" t="s">
         <v>79</v>
       </c>
       <c r="C15" s="9" t="s">
@@ -5038,8 +5047,8 @@
       <c r="AB15" s="9"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A16" s="58"/>
-      <c r="B16" s="59"/>
+      <c r="A16" s="48"/>
+      <c r="B16" s="49"/>
       <c r="C16" s="9" t="s">
         <v>8</v>
       </c>
@@ -5072,8 +5081,8 @@
       <c r="AB16" s="9"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A17" s="58"/>
-      <c r="B17" s="57" t="s">
+      <c r="A17" s="48"/>
+      <c r="B17" s="47" t="s">
         <v>80</v>
       </c>
       <c r="C17" s="9" t="s">
@@ -5108,8 +5117,8 @@
       <c r="AB17" s="9"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A18" s="59"/>
-      <c r="B18" s="59"/>
+      <c r="A18" s="49"/>
+      <c r="B18" s="49"/>
       <c r="C18" s="9" t="s">
         <v>10</v>
       </c>
@@ -5142,10 +5151,10 @@
       <c r="AB18" s="9"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="B19" s="57" t="s">
+      <c r="B19" s="47" t="s">
         <v>82</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -5180,8 +5189,8 @@
       <c r="AB19" s="9"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A20" s="58"/>
-      <c r="B20" s="59"/>
+      <c r="A20" s="48"/>
+      <c r="B20" s="49"/>
       <c r="C20" s="9" t="s">
         <v>12</v>
       </c>
@@ -5214,8 +5223,8 @@
       <c r="AB20" s="9"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A21" s="58"/>
-      <c r="B21" s="57" t="s">
+      <c r="A21" s="48"/>
+      <c r="B21" s="47" t="s">
         <v>83</v>
       </c>
       <c r="C21" s="9" t="s">
@@ -5250,8 +5259,8 @@
       <c r="AB21" s="9"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A22" s="58"/>
-      <c r="B22" s="59"/>
+      <c r="A22" s="48"/>
+      <c r="B22" s="49"/>
       <c r="C22" s="9" t="s">
         <v>14</v>
       </c>
@@ -5284,8 +5293,8 @@
       <c r="AB22" s="9"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A23" s="58"/>
-      <c r="B23" s="57" t="s">
+      <c r="A23" s="48"/>
+      <c r="B23" s="47" t="s">
         <v>84</v>
       </c>
       <c r="C23" s="9" t="s">
@@ -5320,8 +5329,8 @@
       <c r="AB23" s="9"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A24" s="58"/>
-      <c r="B24" s="59"/>
+      <c r="A24" s="48"/>
+      <c r="B24" s="49"/>
       <c r="C24" s="9" t="s">
         <v>16</v>
       </c>
@@ -5354,8 +5363,8 @@
       <c r="AB24" s="9"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A25" s="58"/>
-      <c r="B25" s="57" t="s">
+      <c r="A25" s="48"/>
+      <c r="B25" s="47" t="s">
         <v>85</v>
       </c>
       <c r="C25" s="9" t="s">
@@ -5390,8 +5399,8 @@
       <c r="AB25" s="9"/>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A26" s="59"/>
-      <c r="B26" s="59"/>
+      <c r="A26" s="49"/>
+      <c r="B26" s="49"/>
       <c r="C26" s="9" t="s">
         <v>18</v>
       </c>
@@ -5424,13 +5433,13 @@
       <c r="AB26" s="9"/>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A27" s="57" t="s">
+      <c r="A27" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="49"/>
+      <c r="C27" s="51"/>
       <c r="D27" s="10" t="s">
         <v>70</v>
       </c>
@@ -5460,11 +5469,11 @@
       <c r="AB27" s="9"/>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A28" s="58"/>
-      <c r="B28" s="37" t="s">
+      <c r="A28" s="48"/>
+      <c r="B28" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="39"/>
+      <c r="C28" s="24"/>
       <c r="D28" s="10" t="s">
         <v>71</v>
       </c>
@@ -5494,11 +5503,11 @@
       <c r="AB28" s="9"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A29" s="59"/>
-      <c r="B29" s="60" t="s">
+      <c r="A29" s="49"/>
+      <c r="B29" s="52" t="s">
         <v>89</v>
       </c>
-      <c r="C29" s="61"/>
+      <c r="C29" s="53"/>
       <c r="D29" s="10" t="s">
         <v>72</v>
       </c>
@@ -5529,6 +5538,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A1:D3"/>
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="F2:R3"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="A5:C5"/>
     <mergeCell ref="A27:A29"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B28:C28"/>
@@ -5545,14 +5562,6 @@
     <mergeCell ref="A19:A26"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="B21:B22"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A1:D3"/>
-    <mergeCell ref="S1:V1"/>
-    <mergeCell ref="F2:R3"/>
-    <mergeCell ref="S2:V2"/>
-    <mergeCell ref="A5:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/VanHanhCD1/wwwroot/templates/BMVH_QG1ThieuKet1.xlsx
+++ b/VanHanhCD1/wwwroot/templates/BMVH_QG1ThieuKet1.xlsx
@@ -5,21 +5,30 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\03. Project Hoa Phat\07. Backend\VanHanhCD1_API-main\VanHanhCD1\wwwroot\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02. Du An Hoa Phat\API\VanHanhCD1_API-release\VanHanhCD1\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C1951F-9D03-4C0D-A846-625AF9FF6ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA1776B-D451-477C-B7DA-2BE5CAA121A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1050" windowWidth="14835" windowHeight="15150" activeTab="1" xr2:uid="{749D0495-9471-4B75-B577-F5813F33161C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{749D0495-9471-4B75-B577-F5813F33161C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -318,9 +327,6 @@
     <t>Motor_vibration_OUT_x</t>
   </si>
   <si>
-    <t>Motor_vibration_OUT_y</t>
-  </si>
-  <si>
     <t>Blower_vibration_in_X</t>
   </si>
   <si>
@@ -494,6 +500,9 @@
   </si>
   <si>
     <t>Motor_bearing_temperature_out_232A</t>
+  </si>
+  <si>
+    <t>Motor_vibration_OUT_Y</t>
   </si>
 </sst>
 </file>
@@ -980,10 +989,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1579,7 +1588,7 @@
   <dimension ref="A1:Z35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.85546875" bestFit="1" customWidth="1"/>
@@ -1612,7 +1621,7 @@
     </row>
     <row r="2" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="44" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B2" s="45"/>
       <c r="C2" s="45"/>
@@ -1678,25 +1687,25 @@
         <v>3</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E4" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="G4" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="H4" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="I4" s="17" t="s">
         <v>77</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>78</v>
       </c>
       <c r="J4" s="19"/>
       <c r="K4" s="19"/>
@@ -1705,7 +1714,7 @@
       <c r="N4" s="19"/>
       <c r="O4" s="18"/>
       <c r="P4" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q4" s="19"/>
       <c r="R4" s="19"/>
@@ -1715,7 +1724,7 @@
       <c r="V4" s="19"/>
       <c r="W4" s="18"/>
       <c r="X4" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Y4" s="19"/>
       <c r="Z4" s="18"/>
@@ -1730,42 +1739,42 @@
       <c r="G5" s="40"/>
       <c r="H5" s="40"/>
       <c r="I5" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J5" s="19"/>
       <c r="K5" s="18"/>
       <c r="L5" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M5" s="18"/>
       <c r="N5" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O5" s="18"/>
       <c r="P5" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q5" s="18"/>
       <c r="R5" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S5" s="18"/>
       <c r="T5" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U5" s="18"/>
       <c r="V5" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="W5" s="18"/>
       <c r="X5" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Y5" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z5" s="33" t="s">
         <v>89</v>
-      </c>
-      <c r="Z5" s="33" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="49.5" x14ac:dyDescent="0.25">
@@ -1823,7 +1832,7 @@
         <v>18</v>
       </c>
       <c r="X6" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Y6" s="34"/>
       <c r="Z6" s="34"/>
@@ -4523,7 +4532,7 @@
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
       <c r="S1" s="56" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T1" s="56"/>
       <c r="U1" s="56"/>
@@ -4536,7 +4545,7 @@
       <c r="D2" s="55"/>
       <c r="E2" s="5"/>
       <c r="F2" s="57" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G2" s="57"/>
       <c r="H2" s="57"/>
@@ -4551,7 +4560,7 @@
       <c r="Q2" s="57"/>
       <c r="R2" s="57"/>
       <c r="S2" s="58" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="T2" s="58"/>
       <c r="U2" s="58"/>
@@ -4601,7 +4610,7 @@
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
       <c r="S4" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T4" s="7"/>
       <c r="U4" s="7"/>
@@ -4609,12 +4618,12 @@
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B5" s="60"/>
       <c r="C5" s="61"/>
       <c r="D5" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E5" s="11">
         <v>0.33333333333333331</v>
@@ -4691,7 +4700,7 @@
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" s="50" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B6" s="54"/>
       <c r="C6" s="51"/>
@@ -4727,7 +4736,7 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B7" s="54"/>
       <c r="C7" s="51"/>
@@ -4761,7 +4770,7 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B8" s="23"/>
       <c r="C8" s="24"/>
@@ -4795,7 +4804,7 @@
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9" s="23"/>
       <c r="C9" s="24"/>
@@ -4829,7 +4838,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" s="23"/>
       <c r="C10" s="24"/>
@@ -4863,7 +4872,7 @@
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11" s="23"/>
       <c r="C11" s="24"/>
@@ -4897,10 +4906,10 @@
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="47" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>4</v>
@@ -4934,8 +4943,8 @@
       <c r="AB12" s="9"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="49"/>
-      <c r="B13" s="49"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
       <c r="C13" s="9" t="s">
         <v>5</v>
       </c>
@@ -4968,8 +4977,8 @@
       <c r="AB13" s="9"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="49"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
       <c r="C14" s="9" t="s">
         <v>6</v>
       </c>
@@ -5002,9 +5011,9 @@
       <c r="AB14" s="9"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="49"/>
+      <c r="A15" s="48"/>
       <c r="B15" s="47" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>7</v>
@@ -5038,13 +5047,13 @@
       <c r="AB15" s="9"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A16" s="49"/>
-      <c r="B16" s="48"/>
+      <c r="A16" s="48"/>
+      <c r="B16" s="49"/>
       <c r="C16" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
@@ -5072,9 +5081,9 @@
       <c r="AB16" s="9"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A17" s="49"/>
+      <c r="A17" s="48"/>
       <c r="B17" s="47" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>9</v>
@@ -5108,8 +5117,8 @@
       <c r="AB17" s="9"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
+      <c r="A18" s="49"/>
+      <c r="B18" s="49"/>
       <c r="C18" s="9" t="s">
         <v>10</v>
       </c>
@@ -5143,10 +5152,10 @@
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="47" t="s">
         <v>82</v>
-      </c>
-      <c r="B19" s="47" t="s">
-        <v>83</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>11</v>
@@ -5180,8 +5189,8 @@
       <c r="AB19" s="9"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A20" s="49"/>
-      <c r="B20" s="48"/>
+      <c r="A20" s="48"/>
+      <c r="B20" s="49"/>
       <c r="C20" s="9" t="s">
         <v>12</v>
       </c>
@@ -5214,9 +5223,9 @@
       <c r="AB20" s="9"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A21" s="49"/>
+      <c r="A21" s="48"/>
       <c r="B21" s="47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>13</v>
@@ -5250,13 +5259,13 @@
       <c r="AB21" s="9"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A22" s="49"/>
-      <c r="B22" s="48"/>
+      <c r="A22" s="48"/>
+      <c r="B22" s="49"/>
       <c r="C22" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
@@ -5284,15 +5293,15 @@
       <c r="AB22" s="9"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A23" s="49"/>
+      <c r="A23" s="48"/>
       <c r="B23" s="47" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>15</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
@@ -5320,13 +5329,13 @@
       <c r="AB23" s="9"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A24" s="49"/>
-      <c r="B24" s="48"/>
+      <c r="A24" s="48"/>
+      <c r="B24" s="49"/>
       <c r="C24" s="9" t="s">
         <v>16</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
@@ -5354,15 +5363,15 @@
       <c r="AB24" s="9"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A25" s="49"/>
+      <c r="A25" s="48"/>
       <c r="B25" s="47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
@@ -5390,13 +5399,13 @@
       <c r="AB25" s="9"/>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
+      <c r="A26" s="49"/>
+      <c r="B26" s="49"/>
       <c r="C26" s="9" t="s">
         <v>18</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
@@ -5425,14 +5434,14 @@
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="50" t="s">
         <v>87</v>
-      </c>
-      <c r="B27" s="50" t="s">
-        <v>88</v>
       </c>
       <c r="C27" s="51"/>
       <c r="D27" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
@@ -5460,13 +5469,13 @@
       <c r="AB27" s="9"/>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A28" s="49"/>
+      <c r="A28" s="48"/>
       <c r="B28" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C28" s="24"/>
       <c r="D28" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
@@ -5494,13 +5503,13 @@
       <c r="AB28" s="9"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A29" s="48"/>
+      <c r="A29" s="49"/>
       <c r="B29" s="52" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C29" s="53"/>
       <c r="D29" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
@@ -5529,12 +5538,23 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B25:B26"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A1:D3"/>
     <mergeCell ref="S1:V1"/>
     <mergeCell ref="F2:R3"/>
     <mergeCell ref="S2:V2"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
     <mergeCell ref="A12:A18"/>
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="B15:B16"/>
@@ -5542,17 +5562,6 @@
     <mergeCell ref="A19:A26"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="B21:B22"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
